--- a/data/trans_orig/Q64A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva trabajando en su empresa (en meses)</t>
+          <t>Tiempo medio que lleva trabajando en su empresa (en meses) (tasa de respuesta: 97,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,14; 26,23</t>
+          <t>18,87; 25,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 25,94</t>
+          <t>16,56; 25,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 27,46</t>
+          <t>16,41; 27,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 20,04</t>
+          <t>13,04; 20,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,26</t>
+          <t>13,62; 19,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 25,33</t>
+          <t>16,74; 25,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 26,5</t>
+          <t>16,43; 26,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 22,29</t>
+          <t>13,26; 22,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 22,01</t>
+          <t>17,38; 21,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 23,99</t>
+          <t>17,64; 24,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,43; 24,73</t>
+          <t>17,31; 24,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,95; 19,64</t>
+          <t>14,08; 19,87</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,1; 45,51</t>
+          <t>38,92; 45,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,08; 59,49</t>
+          <t>50,73; 59,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,65; 49,8</t>
+          <t>40,47; 49,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,72; 55,07</t>
+          <t>43,41; 55,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,87; 43,85</t>
+          <t>35,44; 43,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,82; 54,47</t>
+          <t>44,8; 54,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,5; 52,96</t>
+          <t>42,39; 52,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,78; 46,97</t>
+          <t>38,93; 47,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 43,49</t>
+          <t>38,62; 43,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,12; 55,99</t>
+          <t>49,19; 55,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,74; 49,38</t>
+          <t>42,67; 49,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,54; 50,11</t>
+          <t>42,57; 50,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,56; 111,0</t>
+          <t>97,63; 111,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99,67; 114,75</t>
+          <t>99,66; 114,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,97; 107,74</t>
+          <t>93,78; 108,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99,07; 112,56</t>
+          <t>99,42; 112,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,6; 94,55</t>
+          <t>78,01; 95,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,5; 94,13</t>
+          <t>76,37; 94,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,97; 94,27</t>
+          <t>78,39; 94,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,01; 105,29</t>
+          <t>90,82; 104,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,33; 103,48</t>
+          <t>92,6; 103,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,25; 103,9</t>
+          <t>92,44; 104,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,6; 99,76</t>
+          <t>89,82; 100,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,48; 107,14</t>
+          <t>97,65; 107,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>164,08; 186,67</t>
+          <t>164,91; 187,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>161,22; 186,25</t>
+          <t>161,81; 186,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152,56; 178,15</t>
+          <t>153,56; 178,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,12; 188,15</t>
+          <t>49,63; 188,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>101,37; 137,42</t>
+          <t>102,08; 137,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>118,24; 150,93</t>
+          <t>118,29; 150,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>121,31; 150,97</t>
+          <t>121,7; 151,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>133,29; 151,78</t>
+          <t>133,72; 150,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149,34; 169,82</t>
+          <t>149,11; 169,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148,27; 168,62</t>
+          <t>148,68; 168,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143,81; 163,53</t>
+          <t>144,12; 163,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,6; 167,69</t>
+          <t>66,49; 167,88</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>204,0; 248,15</t>
+          <t>206,69; 249,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>267,15; 315,23</t>
+          <t>264,21; 314,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222,92; 268,77</t>
+          <t>219,59; 266,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258,53; 289,35</t>
+          <t>258,39; 289,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>156,5; 226,7</t>
+          <t>156,54; 226,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>129,97; 192,94</t>
+          <t>130,32; 193,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>148,87; 203,71</t>
+          <t>149,57; 201,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>211,21; 242,79</t>
+          <t>210,97; 242,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>200,0; 235,77</t>
+          <t>201,06; 236,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>230,18; 271,87</t>
+          <t>228,76; 271,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197,93; 235,12</t>
+          <t>201,13; 236,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>243,32; 265,75</t>
+          <t>243,1; 266,11</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>253,48; 375,51</t>
+          <t>262,96; 379,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>114,18; 291,53</t>
+          <t>114,18; 293,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>213,39; 322,74</t>
+          <t>211,94; 321,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83,16; 377,91</t>
+          <t>77,81; 370,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>136,79; 296,73</t>
+          <t>143,68; 300,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>250,79; 334,57</t>
+          <t>250,95; 332,75</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>100,34; 109,91</t>
+          <t>100,63; 110,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>120,03; 132,41</t>
+          <t>120,49; 133,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110,99; 123,09</t>
+          <t>110,9; 122,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,02; 145,69</t>
+          <t>81,66; 145,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,85; 78,58</t>
+          <t>67,59; 78,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,29; 92,92</t>
+          <t>80,36; 93,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,53; 97,52</t>
+          <t>85,62; 97,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>98,68; 119,31</t>
+          <t>98,67; 119,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>90,5; 98,07</t>
+          <t>90,55; 98,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105,29; 114,85</t>
+          <t>105,55; 114,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102,3; 111,09</t>
+          <t>102,04; 110,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85,53; 131,89</t>
+          <t>83,53; 131,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,12</t>
+          <t>16,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,71</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>16,34</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 25,6</t>
+          <t>19,14; 26,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 25,78</t>
+          <t>16,5; 25,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 27,1</t>
+          <t>16,15; 26,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,04; 20,38</t>
+          <t>13,34; 19,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,14</t>
+          <t>13,82; 19,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 25,45</t>
+          <t>17,0; 25,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 26,71</t>
+          <t>16,35; 26,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,84</t>
+          <t>13,48; 21,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 21,72</t>
+          <t>17,42; 22,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 24,17</t>
+          <t>17,65; 24,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 24,81</t>
+          <t>17,06; 24,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,08; 19,87</t>
+          <t>13,9; 19,15</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,59</t>
+          <t>47,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,99</t>
+          <t>43,69</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,26</t>
+          <t>45,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,92; 45,43</t>
+          <t>38,85; 45,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,73; 59,69</t>
+          <t>50,26; 59,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,47; 49,85</t>
+          <t>40,18; 49,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,41; 55,57</t>
+          <t>42,69; 53,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,44; 43,85</t>
+          <t>35,4; 44,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,8; 54,11</t>
+          <t>44,48; 54,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,39; 52,79</t>
+          <t>42,58; 53,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,93; 47,09</t>
+          <t>39,68; 47,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 43,68</t>
+          <t>38,35; 43,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,19; 55,81</t>
+          <t>49,32; 55,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,67; 49,73</t>
+          <t>42,74; 49,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,57; 50,01</t>
+          <t>42,33; 49,41</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105,7</t>
+          <t>100,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,02</t>
+          <t>94,25</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>102,43</t>
+          <t>97,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,63; 111,21</t>
+          <t>98,05; 110,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99,66; 114,6</t>
+          <t>99,27; 114,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,78; 108,16</t>
+          <t>93,89; 108,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99,42; 112,7</t>
+          <t>93,69; 106,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 95,61</t>
+          <t>78,24; 95,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,37; 94,46</t>
+          <t>77,29; 94,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,39; 94,6</t>
+          <t>78,72; 94,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,82; 104,5</t>
+          <t>87,98; 100,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,6; 103,19</t>
+          <t>92,78; 103,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,44; 104,04</t>
+          <t>92,23; 104,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,82; 100,29</t>
+          <t>90,21; 100,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,65; 107,29</t>
+          <t>93,15; 102,26</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122,53</t>
+          <t>179,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>142,29</t>
+          <t>139,61</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>129,57</t>
+          <t>161,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>164,91; 187,88</t>
+          <t>164,48; 187,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>161,81; 186,64</t>
+          <t>161,89; 187,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153,56; 178,51</t>
+          <t>153,2; 179,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,63; 188,54</t>
+          <t>169,92; 188,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>102,08; 137,86</t>
+          <t>101,31; 138,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>118,29; 150,79</t>
+          <t>117,84; 150,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>121,7; 151,63</t>
+          <t>121,44; 153,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>133,72; 150,78</t>
+          <t>131,93; 147,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149,11; 169,29</t>
+          <t>149,61; 170,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148,68; 168,87</t>
+          <t>148,02; 167,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144,12; 163,58</t>
+          <t>144,51; 164,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,49; 167,88</t>
+          <t>155,26; 168,49</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273,96</t>
+          <t>263,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>226,5</t>
+          <t>222,87</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>254,47</t>
+          <t>246,53</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>206,69; 249,66</t>
+          <t>205,3; 249,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>264,21; 314,46</t>
+          <t>263,3; 313,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219,59; 266,64</t>
+          <t>223,21; 268,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258,39; 289,34</t>
+          <t>246,27; 279,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>156,54; 226,29</t>
+          <t>152,38; 228,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>130,32; 193,93</t>
+          <t>128,84; 193,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>149,57; 201,12</t>
+          <t>150,88; 205,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>210,97; 242,26</t>
+          <t>207,64; 237,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>201,06; 236,98</t>
+          <t>199,28; 234,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228,76; 271,44</t>
+          <t>229,59; 271,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201,13; 236,41</t>
+          <t>200,51; 236,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>243,1; 266,11</t>
+          <t>235,63; 258,39</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>323,53</t>
+          <t>305,86</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>264,77</t>
+          <t>264,85</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>294,86</t>
+          <t>286,04</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,32; 333,28</t>
+          <t>100,87; 344,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>262,96; 379,57</t>
+          <t>238,25; 364,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>211,94; 321,67</t>
+          <t>208,21; 323,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77,81; 370,88</t>
+          <t>82,38; 356,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>199,16; 440,04</t>
+          <t>203,26; 442,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>143,68; 300,43</t>
+          <t>138,82; 293,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>250,95; 332,75</t>
+          <t>243,21; 330,03</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>387,14</t>
+          <t>373,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>387,14</t>
+          <t>373,54</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125,25</t>
+          <t>136,69</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113,16</t>
+          <t>114,09</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120,19</t>
+          <t>126,8</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>100,63; 110,69</t>
+          <t>100,94; 110,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>120,49; 133,35</t>
+          <t>119,12; 132,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110,9; 122,97</t>
+          <t>111,33; 123,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,66; 145,29</t>
+          <t>130,74; 142,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,59; 78,73</t>
+          <t>67,54; 78,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,36; 93,07</t>
+          <t>80,14; 92,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,62; 97,52</t>
+          <t>85,77; 97,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>98,67; 119,3</t>
+          <t>108,99; 119,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>90,55; 98,13</t>
+          <t>90,49; 98,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105,55; 114,71</t>
+          <t>105,17; 114,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102,04; 110,7</t>
+          <t>101,7; 110,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,53; 131,26</t>
+          <t>122,73; 131,03</t>
         </is>
       </c>
     </row>
